--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260323_203207.xlsx
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
